--- a/tests/TC-15/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-15/results/timetable_all_departments_even.xlsx
@@ -78,6 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFDAB3"/>
         <bgColor rgb="00FFDAB3"/>
       </patternFill>
@@ -90,20 +96,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0E6"/>
-        <bgColor rgb="00FFD0E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF3BF"/>
         <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,14 +155,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -194,19 +194,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,16 +222,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -839,147 +839,227 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
+          <t>CS2
+LEC
+Room: 110
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>CS1
+TUT
+Room: 106
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr"/>
+      <c r="J2" s="12" t="inlineStr"/>
+      <c r="K2" s="12" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS3
+LEC
+Room: 101
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="n"/>
+      <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="12" t="inlineStr"/>
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+TUT
+Room: 101
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr"/>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>CS4
+LEC
+Room: 103
+Dr. Prof4</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr"/>
+      <c r="N3" s="12" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>CS1
+LEC
+Room: 101
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="12" t="inlineStr"/>
+      <c r="H4" s="12" t="inlineStr"/>
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
           <t>CS3
 TUT
-Room: 109
+Room: 110
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-TUT
-Room: 109
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="14" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 110
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="12" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr"/>
+      <c r="Q4" s="12" t="inlineStr"/>
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr"/>
+      <c r="T4" s="12" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>CS3
+LEC
+Room: 101
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="12" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>CS4
 TUT
-Room: 103
+Room: 110
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 110
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="12" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>CS1
 LEC
-Room: 105
+Room: 101
 Dr. Prof1</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>CS3
-LEC
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 102
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>CS3
-LEC
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="12" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>CS2
 TUT
@@ -987,139 +1067,59 @@
 Dr. Prof2</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>CS2
+LEC
+Room: 110
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>CS4
 LEC
-Room: 110
+Room: 103
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-TUT
-Room: 109
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>CS4
-LEC
-Room: 110
-Dr. Prof4</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-LEC
-Room: 105
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 102
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="12" t="inlineStr"/>
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr"/>
+      <c r="T6" s="12" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1301,22 +1301,24 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>110</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="P5:R5"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="N6:P6"/>
     <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1476,147 +1478,227 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
+          <t>CS2
+LEC
+Room: 110
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>CS1
+TUT
+Room: 106
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr"/>
+      <c r="J2" s="12" t="inlineStr"/>
+      <c r="K2" s="12" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS3
+LEC
+Room: 101
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="n"/>
+      <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="12" t="inlineStr"/>
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+TUT
+Room: 101
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr"/>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>CS4
+LEC
+Room: 103
+Dr. Prof4</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr"/>
+      <c r="N3" s="12" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>CS1
+LEC
+Room: 101
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="12" t="inlineStr"/>
+      <c r="H4" s="12" t="inlineStr"/>
+      <c r="I4" s="12" t="inlineStr"/>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
           <t>CS3
 TUT
-Room: 109
+Room: 110
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-TUT
-Room: 109
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="14" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 110
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="12" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr"/>
+      <c r="Q4" s="12" t="inlineStr"/>
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr"/>
+      <c r="T4" s="12" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>CS3
+LEC
+Room: 101
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="12" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>CS4
 TUT
-Room: 103
+Room: 110
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 110
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="12" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>CS1
 LEC
-Room: 105
+Room: 101
 Dr. Prof1</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>CS3
-LEC
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 102
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>CS3
-LEC
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="12" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>CS2
 TUT
@@ -1624,139 +1706,59 @@
 Dr. Prof2</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>CS2
+LEC
+Room: 110
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>CS4
 LEC
-Room: 110
+Room: 103
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-TUT
-Room: 109
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>CS4
-LEC
-Room: 110
-Dr. Prof4</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-LEC
-Room: 105
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 102
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="12" t="inlineStr"/>
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr"/>
+      <c r="T6" s="12" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1826,7 +1828,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1856,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1884,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1912,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1938,22 +1940,24 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>110</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="P5:R5"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="N6:P6"/>
     <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1966,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2021,29 +2025,29 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -2069,12 +2073,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2090,13 +2094,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2129,19 +2133,19 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2151,7 +2155,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS4</t>
         </is>
       </c>
     </row>
@@ -2162,22 +2166,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2201,14 +2205,14 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2218,12 +2222,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2234,17 +2238,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2259,7 +2263,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
@@ -2273,19 +2277,19 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Prof2</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2295,7 +2299,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2309,29 +2313,29 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS4</t>
         </is>
       </c>
     </row>
@@ -2345,10 +2349,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2357,7 +2361,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2378,22 +2382,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Prof2</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2403,69 +2407,69 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSE_4_B</t>
+          <t>CSE_4_A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSE_4_B</t>
+          <t>CSE_4_A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2475,7 +2479,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS4</t>
         </is>
       </c>
     </row>
@@ -2486,17 +2490,17 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>13</v>
-      </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
@@ -2522,32 +2526,32 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2558,13 +2562,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2594,13 +2598,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2609,7 +2613,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2630,22 +2634,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2655,7 +2659,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2666,32 +2670,32 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Prof2</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2706,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>13</v>
@@ -2712,12 +2716,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2727,7 +2731,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2745,19 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2763,7 +2767,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2774,32 +2778,176 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dr. Prof4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>6</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>6</v>
       </c>
-      <c r="D23" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="C27" t="n">
+        <v>14</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dr. Prof4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>LEC</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>CS2</t>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CS4</t>
         </is>
       </c>
     </row>

--- a/tests/TC-15/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-15/results/timetable_all_departments_even.xlsx
@@ -84,12 +84,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
@@ -104,6 +98,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD0E6"/>
         <bgColor rgb="00FFD0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,14 +155,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -194,19 +194,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,7 +222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,10 +231,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -837,49 +837,49 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>CS2
 LEC
-Room: 110
+Room: 108
 Dr. Prof2</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-TUT
-Room: 106
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="12" t="inlineStr"/>
-      <c r="I2" s="12" t="inlineStr"/>
-      <c r="J2" s="12" t="inlineStr"/>
-      <c r="K2" s="12" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>CS3
 LEC
-Room: 101
+Room: 102
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="12" t="inlineStr"/>
-      <c r="R2" s="12" t="inlineStr"/>
-      <c r="S2" s="12" t="inlineStr"/>
-      <c r="T2" s="12" t="inlineStr"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>CS5
+TUT
+Room: 102
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -898,16 +898,6 @@
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-TUT
-Room: 101
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr"/>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>CS4
 LEC
@@ -915,31 +905,41 @@
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="12" t="inlineStr"/>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>CS2
+LEC
+Room: 108
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr"/>
-      <c r="N3" s="12" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr"/>
-      <c r="P3" s="12" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>CS1
 LEC
-Room: 101
+Room: 103
 Dr. Prof1</t>
         </is>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="9" t="n"/>
-      <c r="T3" s="12" t="inlineStr"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -957,156 +957,45 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="12" t="inlineStr"/>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>CS3
-TUT
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>CS5
 LEC
-Room: 110
+Room: 102
 Dr. Prof5</t>
         </is>
       </c>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="12" t="inlineStr"/>
-      <c r="P4" s="12" t="inlineStr"/>
-      <c r="Q4" s="12" t="inlineStr"/>
-      <c r="R4" s="12" t="inlineStr"/>
-      <c r="S4" s="12" t="inlineStr"/>
-      <c r="T4" s="12" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>CS1
+LEC
+Room: 103
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>CS3
 LEC
-Room: 101
+Room: 102
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>CS4
-TUT
-Room: 110
-Dr. Prof4</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 110
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="12" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-LEC
-Room: 101
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="12" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>CS2
-TUT
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 110
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="12" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr"/>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="15" t="inlineStr">
         <is>
           <t>CS4
 LEC
@@ -1114,12 +1003,123 @@
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="12" t="inlineStr"/>
-      <c r="R6" s="12" t="inlineStr"/>
-      <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="12" t="inlineStr"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CS2
+TUT
+Room: 105
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>CS1
+TUT
+Room: 108
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>CS3
+TUT
+Room: 105
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 102
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>CS4
+TUT
+Room: 104
+Dr. Prof4</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1301,25 +1301,24 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="J4:K4"/>
+  <mergeCells count="12">
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1476,49 +1475,49 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>CS2
 LEC
-Room: 110
+Room: 108
 Dr. Prof2</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-TUT
-Room: 106
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="12" t="inlineStr"/>
-      <c r="I2" s="12" t="inlineStr"/>
-      <c r="J2" s="12" t="inlineStr"/>
-      <c r="K2" s="12" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>CS3
 LEC
-Room: 101
+Room: 102
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="12" t="inlineStr"/>
-      <c r="R2" s="12" t="inlineStr"/>
-      <c r="S2" s="12" t="inlineStr"/>
-      <c r="T2" s="12" t="inlineStr"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>CS5
+TUT
+Room: 102
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1537,16 +1536,6 @@
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-TUT
-Room: 101
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr"/>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>CS4
 LEC
@@ -1554,31 +1543,41 @@
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="12" t="inlineStr"/>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>CS2
+LEC
+Room: 108
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr"/>
-      <c r="N3" s="12" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr"/>
-      <c r="P3" s="12" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>CS1
 LEC
-Room: 101
+Room: 103
 Dr. Prof1</t>
         </is>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="9" t="n"/>
-      <c r="T3" s="12" t="inlineStr"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1596,156 +1595,45 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="12" t="inlineStr"/>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="12" t="inlineStr"/>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>CS3
-TUT
-Room: 110
-Dr. Prof3</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>CS5
 LEC
-Room: 110
+Room: 102
 Dr. Prof5</t>
         </is>
       </c>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="12" t="inlineStr"/>
-      <c r="P4" s="12" t="inlineStr"/>
-      <c r="Q4" s="12" t="inlineStr"/>
-      <c r="R4" s="12" t="inlineStr"/>
-      <c r="S4" s="12" t="inlineStr"/>
-      <c r="T4" s="12" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>CS1
+LEC
+Room: 103
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>CS3
 LEC
-Room: 101
+Room: 102
 Dr. Prof3</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>CS4
-TUT
-Room: 110
-Dr. Prof4</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>CS5
-LEC
-Room: 110
-Dr. Prof5</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="12" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr">
-        <is>
-          <t>CS1
-LEC
-Room: 101
-Dr. Prof1</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="12" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>CS2
-TUT
-Room: 107
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>CS2
-LEC
-Room: 110
-Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="12" t="inlineStr"/>
-      <c r="J6" s="12" t="inlineStr"/>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="15" t="inlineStr">
         <is>
           <t>CS4
 LEC
@@ -1753,12 +1641,123 @@
 Dr. Prof4</t>
         </is>
       </c>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="12" t="inlineStr"/>
-      <c r="R6" s="12" t="inlineStr"/>
-      <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="12" t="inlineStr"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CS2
+TUT
+Room: 105
+Dr. Prof2</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>CS1
+TUT
+Room: 108
+Dr. Prof1</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>CS3
+TUT
+Room: 105
+Dr. Prof3</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>CS5
+LEC
+Room: 102
+Dr. Prof5</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>CS4
+TUT
+Room: 104
+Dr. Prof4</t>
+        </is>
+      </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1828,7 +1827,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1855,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1883,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1940,25 +1939,24 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="J4:K4"/>
+  <mergeCells count="12">
+    <mergeCell ref="H6:J6"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1970,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2025,10 +2023,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2037,7 +2035,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2061,29 +2059,29 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2097,29 +2095,29 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2131,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2169,19 +2167,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2191,7 +2189,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2200,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2241,10 +2239,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2253,7 +2251,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2274,22 +2272,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2299,7 +2297,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2310,32 +2308,32 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2346,22 +2344,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2371,7 +2369,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS4</t>
         </is>
       </c>
     </row>
@@ -2382,13 +2380,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2397,12 +2395,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2421,19 +2419,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Prof2</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2443,33 +2441,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2479,7 +2477,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
@@ -2493,19 +2491,19 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Prof2</t>
+          <t>Dr. Prof3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2515,7 +2513,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>CS3</t>
         </is>
       </c>
     </row>
@@ -2529,19 +2527,19 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2551,7 +2549,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS1</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
@@ -2562,22 +2560,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2587,7 +2585,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS4</t>
         </is>
       </c>
     </row>
@@ -2601,19 +2599,19 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Prof4</t>
+          <t>Dr. Prof2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2623,7 +2621,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CS4</t>
+          <t>CS2</t>
         </is>
       </c>
     </row>
@@ -2637,10 +2635,10 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2649,7 +2647,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2673,29 +2671,29 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Prof3</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CS3</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
@@ -2709,19 +2707,19 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2731,7 +2729,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2742,13 +2740,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2778,13 +2776,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2793,12 +2791,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2814,32 +2812,32 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Prof5</t>
+          <t>Dr. Prof1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS5</t>
+          <t>CS1</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2848,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
         <v>16</v>
@@ -2860,12 +2858,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dr. Prof1</t>
+          <t>Dr. Prof5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2875,79 +2873,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Dr. Prof2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" t="n">
-        <v>14</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Dr. Prof4</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>CS4</t>
+          <t>CS5</t>
         </is>
       </c>
     </row>
